--- a/Money_Balance_V5/Money_balance.xlsx
+++ b/Money_Balance_V5/Money_balance.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
   <si>
     <t>Valued_stuff</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Balance, too much spending in Jan, New celphone and flight tickets in last day.</t>
+  </si>
+  <si>
+    <t>Onde day before day 10</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1876,7 +1879,7 @@
         <v>48900.53</v>
       </c>
       <c r="D69">
-        <f t="shared" ref="D69:D71" si="0">B69+C69</f>
+        <f t="shared" ref="D69:D72" si="0">B69+C69</f>
         <v>88900.53</v>
       </c>
       <c r="E69" s="1">
@@ -1926,6 +1929,27 @@
       </c>
       <c r="F71" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72">
+        <v>7800</v>
+      </c>
+      <c r="B72">
+        <v>40000</v>
+      </c>
+      <c r="C72">
+        <v>52872.14</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="0"/>
+        <v>92872.14</v>
+      </c>
+      <c r="E72" s="1">
+        <v>46063</v>
+      </c>
+      <c r="F72" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Money_Balance_V5/Money_balance.xlsx
+++ b/Money_Balance_V5/Money_balance.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>Valued_stuff</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Onde day before day 10</t>
+  </si>
+  <si>
+    <t>Onde day before day 10, solved car parts</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1946,10 +1949,31 @@
         <v>92872.14</v>
       </c>
       <c r="E72" s="1">
-        <v>46063</v>
+        <v>46091</v>
       </c>
       <c r="F72" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73">
+        <v>7800</v>
+      </c>
+      <c r="B73">
+        <v>43000</v>
+      </c>
+      <c r="C73">
+        <v>53915.22</v>
+      </c>
+      <c r="D73">
+        <f t="shared" ref="D73" si="1">B73+C73</f>
+        <v>96915.22</v>
+      </c>
+      <c r="E73" s="1">
+        <v>46122</v>
+      </c>
+      <c r="F73" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Money_Balance_V5/Money_balance.xlsx
+++ b/Money_Balance_V5/Money_balance.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
   <si>
     <t>Valued_stuff</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Onde day before day 10, solved car parts</t>
+  </si>
+  <si>
+    <t>No significant input</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1966,7 +1969,7 @@
         <v>53915.22</v>
       </c>
       <c r="D73">
-        <f t="shared" ref="D73" si="1">B73+C73</f>
+        <f t="shared" ref="D73:D74" si="1">B73+C73</f>
         <v>96915.22</v>
       </c>
       <c r="E73" s="1">
@@ -1974,6 +1977,27 @@
       </c>
       <c r="F73" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74">
+        <v>7800</v>
+      </c>
+      <c r="B74">
+        <v>43000</v>
+      </c>
+      <c r="C74">
+        <v>54931.74</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="1"/>
+        <v>97931.739999999991</v>
+      </c>
+      <c r="E74" s="1">
+        <v>46152</v>
+      </c>
+      <c r="F74" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Money_Balance_V5/Money_balance.xlsx
+++ b/Money_Balance_V5/Money_balance.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>Valued_stuff</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>No significant input</t>
+  </si>
+  <si>
+    <t>Change to Belem city</t>
   </si>
 </sst>
 </file>
@@ -504,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1969,7 +1972,7 @@
         <v>53915.22</v>
       </c>
       <c r="D73">
-        <f t="shared" ref="D73:D74" si="1">B73+C73</f>
+        <f t="shared" ref="D73:D75" si="1">B73+C73</f>
         <v>96915.22</v>
       </c>
       <c r="E73" s="1">
@@ -1998,6 +2001,27 @@
       </c>
       <c r="F74" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75">
+        <v>7800</v>
+      </c>
+      <c r="B75">
+        <v>43000</v>
+      </c>
+      <c r="C75">
+        <v>56607.14</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="1"/>
+        <v>99607.14</v>
+      </c>
+      <c r="E75" s="1">
+        <v>46183</v>
+      </c>
+      <c r="F75" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Money_Balance_V5/Money_balance.xlsx
+++ b/Money_Balance_V5/Money_balance.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="54">
   <si>
     <t>Valued_stuff</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>Change to Belem city</t>
+  </si>
+  <si>
+    <t>Finally six digits</t>
   </si>
 </sst>
 </file>
@@ -224,9 +227,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1794,7 +1798,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>5200</v>
       </c>
@@ -1814,7 +1818,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>5200</v>
       </c>
@@ -1835,7 +1839,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>5200</v>
       </c>
@@ -1856,7 +1860,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>5200</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>7800</v>
       </c>
@@ -1898,7 +1902,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>7800</v>
       </c>
@@ -1919,7 +1923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>7800</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>7800</v>
       </c>
@@ -1961,7 +1965,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>7800</v>
       </c>
@@ -1972,7 +1976,7 @@
         <v>53915.22</v>
       </c>
       <c r="D73">
-        <f t="shared" ref="D73:D75" si="1">B73+C73</f>
+        <f t="shared" ref="D73:D76" si="1">B73+C73</f>
         <v>96915.22</v>
       </c>
       <c r="E73" s="1">
@@ -1982,7 +1986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>7800</v>
       </c>
@@ -2003,7 +2007,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>7800</v>
       </c>
@@ -2022,6 +2026,49 @@
       </c>
       <c r="F75" t="s">
         <v>52</v>
+      </c>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76">
+        <v>7800</v>
+      </c>
+      <c r="B76">
+        <v>43000</v>
+      </c>
+      <c r="C76">
+        <v>56607.14</v>
+      </c>
+      <c r="D76">
+        <f t="shared" ref="D76" si="2">B76+C76</f>
+        <v>99607.14</v>
+      </c>
+      <c r="E76" s="1">
+        <v>46213</v>
+      </c>
+      <c r="F76" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77">
+        <v>7800</v>
+      </c>
+      <c r="B77">
+        <v>43000</v>
+      </c>
+      <c r="C77">
+        <v>62894.99</v>
+      </c>
+      <c r="D77">
+        <f>B77+C77</f>
+        <v>105894.98999999999</v>
+      </c>
+      <c r="E77" s="1">
+        <v>46244</v>
+      </c>
+      <c r="F77" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
